--- a/r4-ELGA-IV-Diabetes-fokuswoche/StructureDefinition-MedicalDevices-ips.xlsx
+++ b/r4-ELGA-IV-Diabetes-fokuswoche/StructureDefinition-MedicalDevices-ips.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T14:25:12+00:00</t>
+    <t>2024-12-17T15:13:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-fokuswoche/StructureDefinition-MedicalDevices-ips.xlsx
+++ b/r4-ELGA-IV-Diabetes-fokuswoche/StructureDefinition-MedicalDevices-ips.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-17T15:13:00+00:00</t>
+    <t>2024-12-20T15:32:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-fokuswoche/StructureDefinition-MedicalDevices-ips.xlsx
+++ b/r4-ELGA-IV-Diabetes-fokuswoche/StructureDefinition-MedicalDevices-ips.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-20T15:32:12+00:00</t>
+    <t>2024-12-20T15:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
